--- a/public/downloads/MandalMetal2024.xlsx
+++ b/public/downloads/MandalMetal2024.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="53">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -165,6 +167,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>CH</t>
@@ -653,10 +676,10 @@
         <v>356</v>
       </c>
       <c r="N3" s="5">
-        <v>1907.147875785828</v>
+        <v>1907147.875785828</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03348458241073509</v>
+        <v>33.48458241073509</v>
       </c>
       <c r="P3" s="5">
         <v>56956</v>
@@ -703,10 +726,10 @@
         <v>356</v>
       </c>
       <c r="N4" s="5">
-        <v>4296.561753988266</v>
+        <v>4296561.753988266</v>
       </c>
       <c r="O4" s="4">
-        <v>0.06291088429759087</v>
+        <v>62.91088429759087</v>
       </c>
       <c r="P4" s="5">
         <v>68296</v>
@@ -753,10 +776,10 @@
         <v>356</v>
       </c>
       <c r="N5" s="5">
-        <v>6543.797536373138</v>
+        <v>6543797.536373138</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1350071701335494</v>
+        <v>135.0071701335494</v>
       </c>
       <c r="P5" s="5">
         <v>48470</v>
@@ -803,10 +826,10 @@
         <v>356</v>
       </c>
       <c r="N6" s="5">
-        <v>4669.980201721191</v>
+        <v>4669980.201721191</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08570500838189711</v>
+        <v>85.70500838189712</v>
       </c>
       <c r="P6" s="5">
         <v>54489</v>
@@ -853,10 +876,10 @@
         <v>356</v>
       </c>
       <c r="N7" s="5">
-        <v>11382.74066781998</v>
+        <v>11382740.66781998</v>
       </c>
       <c r="O7" s="4">
-        <v>0.2433873731572865</v>
+        <v>243.3873731572865</v>
       </c>
       <c r="P7" s="5">
         <v>46768</v>
@@ -903,10 +926,10 @@
         <v>356</v>
       </c>
       <c r="N8" s="5">
-        <v>886.133695602417</v>
+        <v>886133.695602417</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01760087585115832</v>
+        <v>17.60087585115832</v>
       </c>
       <c r="P8" s="5">
         <v>50346</v>
@@ -953,10 +976,10 @@
         <v>356</v>
       </c>
       <c r="N9" s="5">
-        <v>2093.47083902359</v>
+        <v>2093470.83902359</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03126963567825643</v>
+        <v>31.26963567825644</v>
       </c>
       <c r="P9" s="5">
         <v>66949</v>
@@ -1003,10 +1026,10 @@
         <v>356</v>
       </c>
       <c r="N10" s="5">
-        <v>3715.791021585464</v>
+        <v>3715791.021585464</v>
       </c>
       <c r="O10" s="4">
-        <v>0.09030966147977797</v>
+        <v>90.30966147977797</v>
       </c>
       <c r="P10" s="5">
         <v>41145</v>
@@ -1053,10 +1076,10 @@
         <v>356</v>
       </c>
       <c r="N11" s="5">
-        <v>2472.570067644119</v>
+        <v>2472570.067644119</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04127416398431074</v>
+        <v>41.27416398431074</v>
       </c>
       <c r="P11" s="5">
         <v>59906</v>
@@ -1103,10 +1126,10 @@
         <v>356</v>
       </c>
       <c r="N12" s="5">
-        <v>1000.044785499573</v>
+        <v>1000044.785499573</v>
       </c>
       <c r="O12" s="4">
-        <v>0.02119277751758016</v>
+        <v>21.19277751758016</v>
       </c>
       <c r="P12" s="5">
         <v>47188</v>
@@ -1153,10 +1176,10 @@
         <v>356</v>
       </c>
       <c r="N13" s="5">
-        <v>4975.748042583466</v>
+        <v>4975748.042583466</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07785554752907942</v>
+        <v>77.85554752907942</v>
       </c>
       <c r="P13" s="5">
         <v>63910</v>
@@ -1203,10 +1226,10 @@
         <v>75</v>
       </c>
       <c r="N14" s="5">
-        <v>5024.593505620956</v>
+        <v>5024593.505620956</v>
       </c>
       <c r="O14" s="4">
-        <v>0.3450483110576127</v>
+        <v>345.0483110576128</v>
       </c>
       <c r="P14" s="5">
         <v>14562</v>
@@ -1253,10 +1276,10 @@
         <v>75</v>
       </c>
       <c r="N15" s="5">
-        <v>5689.96302986145</v>
+        <v>5689963.02986145</v>
       </c>
       <c r="O15" s="4">
-        <v>0.3310427641297097</v>
+        <v>331.0427641297097</v>
       </c>
       <c r="P15" s="5">
         <v>17188</v>
@@ -1303,10 +1326,10 @@
         <v>75</v>
       </c>
       <c r="N16" s="5">
-        <v>1012.192121982574</v>
+        <v>1012192.121982574</v>
       </c>
       <c r="O16" s="4">
-        <v>0.09849101118834042</v>
+        <v>98.49101118834042</v>
       </c>
       <c r="P16" s="5">
         <v>10277</v>
@@ -1353,10 +1376,10 @@
         <v>75</v>
       </c>
       <c r="N17" s="5">
-        <v>2151.973101377487</v>
+        <v>2151973.101377487</v>
       </c>
       <c r="O17" s="4">
-        <v>0.09897769760728024</v>
+        <v>98.97769760728025</v>
       </c>
       <c r="P17" s="5">
         <v>21742</v>
@@ -1384,7 +1407,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1395,9 +1418,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1431,8 +1460,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1454,50 +1491,86 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.7979585431680768</v>
+        <v>1.083794477503847</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3351135331373916</v>
+        <v>0.9931274365916724</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4261519876850648</v>
+        <v>1.025895669623709</v>
       </c>
       <c r="E3" s="4">
-        <v>80.59682539682504</v>
+        <v>82.70249433106626</v>
       </c>
       <c r="F3" s="4">
-        <v>75.43176733780875</v>
+        <v>73.44310216256507</v>
       </c>
       <c r="G3" s="5">
         <v>75</v>
       </c>
       <c r="H3" s="5">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I3" s="5">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="J3" s="5">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K3" s="5">
         <v>2</v>
       </c>
       <c r="L3" s="5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>0.9931274365916724</v>
+      </c>
+      <c r="O3" s="5">
+        <v>44</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.9737027997801503</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2363680394090351</v>
+      </c>
+      <c r="R3" s="5">
+        <v>44</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1508,6 +1581,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1515,7 +1589,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1526,9 +1600,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1562,8 +1642,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1585,50 +1673,86 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.18801483974574</v>
+        <v>1.166632073732801</v>
       </c>
       <c r="C3" s="4">
-        <v>1.298505031344896</v>
+        <v>1.068705100845164</v>
       </c>
       <c r="D3" s="4">
-        <v>1.344631318788903</v>
+        <v>1.038358367027022</v>
       </c>
       <c r="E3" s="4">
-        <v>82.70975056689352</v>
+        <v>78.26848072562331</v>
       </c>
       <c r="F3" s="4">
-        <v>74.70290827740411</v>
+        <v>68.55615212527937</v>
       </c>
       <c r="G3" s="5">
         <v>75</v>
       </c>
       <c r="H3" s="5">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="I3" s="5">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J3" s="5">
+        <v>17</v>
+      </c>
+      <c r="K3" s="5">
+        <v>5</v>
+      </c>
+      <c r="L3" s="5">
         <v>12</v>
       </c>
-      <c r="K3" s="5">
-        <v>7</v>
-      </c>
-      <c r="L3" s="5">
-        <v>4</v>
-      </c>
       <c r="M3" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>1.068705100845164</v>
+      </c>
+      <c r="O3" s="5">
+        <v>37</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.236968312849004</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2947446408733825</v>
+      </c>
+      <c r="R3" s="5">
+        <v>37</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1639,6 +1763,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1646,7 +1771,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1657,9 +1782,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1693,8 +1824,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1716,50 +1855,86 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.019797500282196</v>
+        <v>0.7979585431680768</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2267594442163123</v>
+        <v>0.3351135331373916</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2473488068438499</v>
+        <v>0.4261519876850648</v>
       </c>
       <c r="E3" s="4">
-        <v>78.46394557823085</v>
+        <v>80.59682539682504</v>
       </c>
       <c r="F3" s="4">
-        <v>70.25906040268416</v>
+        <v>75.43176733780875</v>
       </c>
       <c r="G3" s="5">
         <v>75</v>
       </c>
       <c r="H3" s="5">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="I3" s="5">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="J3" s="5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K3" s="5">
         <v>2</v>
       </c>
       <c r="L3" s="5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>0.3351135331373916</v>
+      </c>
+      <c r="O3" s="5">
+        <v>49</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7691834243171369</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1406108465487569</v>
+      </c>
+      <c r="R3" s="5">
+        <v>49</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1770,6 +1945,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1777,7 +1953,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1788,9 +1964,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1824,8 +2006,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1847,50 +2037,86 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.055809624690695</v>
+        <v>1.18801483974574</v>
       </c>
       <c r="C3" s="4">
-        <v>0.7130821895449037</v>
+        <v>1.298505031344896</v>
       </c>
       <c r="D3" s="4">
-        <v>0.7548184233319533</v>
+        <v>1.344631318788903</v>
       </c>
       <c r="E3" s="4">
-        <v>81.36961451247205</v>
+        <v>82.70975056689352</v>
       </c>
       <c r="F3" s="4">
-        <v>70.0165548098425</v>
+        <v>74.70290827740411</v>
       </c>
       <c r="G3" s="5">
         <v>75</v>
       </c>
       <c r="H3" s="5">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I3" s="5">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J3" s="5">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K3" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L3" s="5">
         <v>4</v>
       </c>
       <c r="M3" s="5">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4">
+        <v>1.314934356725868</v>
+      </c>
+      <c r="O3" s="5">
+        <v>46</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.9812917549114208</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2288222077984503</v>
+      </c>
+      <c r="R3" s="5">
+        <v>46</v>
+      </c>
+      <c r="S3" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1901,6 +2127,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1908,7 +2135,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1919,9 +2146,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1955,8 +2188,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1978,50 +2219,86 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6599321517950693</v>
+        <v>1.019797500282196</v>
       </c>
       <c r="C3" s="4">
-        <v>0.06541270918783788</v>
+        <v>0.2267594442163123</v>
       </c>
       <c r="D3" s="4">
-        <v>0.09038220533550712</v>
+        <v>0.2473488068438499</v>
       </c>
       <c r="E3" s="4">
-        <v>90.18231292517036</v>
+        <v>78.46394557823085</v>
       </c>
       <c r="F3" s="4">
-        <v>80.54213273676372</v>
+        <v>70.25906040268416</v>
       </c>
       <c r="G3" s="5">
         <v>75</v>
       </c>
       <c r="H3" s="5">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="I3" s="5">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J3" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" s="5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>0.166217374891215</v>
+      </c>
+      <c r="O3" s="5">
+        <v>41</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.064570208689268</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1708219413926307</v>
+      </c>
+      <c r="R3" s="5">
+        <v>41</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2032,6 +2309,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2039,7 +2317,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2050,9 +2328,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2086,8 +2370,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2109,34 +2401,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.724274470268531</v>
+        <v>1.055809624690695</v>
       </c>
       <c r="C3" s="4">
-        <v>0.7844856922489294</v>
+        <v>0.7130821895449037</v>
       </c>
       <c r="D3" s="4">
-        <v>0.7625621607490705</v>
+        <v>0.7548184233319533</v>
       </c>
       <c r="E3" s="4">
-        <v>80.24943310657621</v>
+        <v>81.36961451247205</v>
       </c>
       <c r="F3" s="4">
-        <v>73.03758389261823</v>
+        <v>70.0165548098425</v>
       </c>
       <c r="G3" s="5">
         <v>75</v>
       </c>
       <c r="H3" s="5">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="I3" s="5">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J3" s="5">
         <v>9</v>
@@ -2150,9 +2460,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>0.7130821895449037</v>
+      </c>
+      <c r="O3" s="5">
+        <v>39</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.046928913703544</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1292336152671493</v>
+      </c>
+      <c r="R3" s="5">
+        <v>39</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2163,6 +2491,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2170,7 +2499,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2181,9 +2510,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2217,8 +2552,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2240,50 +2583,86 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6001724841333852</v>
+        <v>0.6599321517950693</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1010085558963831</v>
+        <v>0.06541270918783788</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1078919592197236</v>
+        <v>0.09038220533550712</v>
       </c>
       <c r="E3" s="4">
-        <v>89.58594104308442</v>
+        <v>90.18231292517036</v>
       </c>
       <c r="F3" s="4">
-        <v>81.89395973154329</v>
+        <v>80.54213273676372</v>
       </c>
       <c r="G3" s="5">
         <v>75</v>
       </c>
       <c r="H3" s="5">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I3" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J3" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K3" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.01348957171501533</v>
+      </c>
+      <c r="O3" s="5">
+        <v>49</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.654106167967941</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.06310252416999571</v>
+      </c>
+      <c r="R3" s="5">
+        <v>49</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2294,6 +2673,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2301,7 +2681,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2312,9 +2692,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2348,8 +2734,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2371,25 +2765,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.148473520582814</v>
+        <v>1.724274470268531</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1592879273323103</v>
+        <v>0.7844856922489294</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1256895090637306</v>
+        <v>0.7625621607490705</v>
       </c>
       <c r="E3" s="4">
-        <v>78.68843537414952</v>
+        <v>80.24943310657621</v>
       </c>
       <c r="F3" s="4">
-        <v>71.92975391498962</v>
+        <v>73.03758389261823</v>
       </c>
       <c r="G3" s="5">
         <v>75</v>
@@ -2404,17 +2816,35 @@
         <v>9</v>
       </c>
       <c r="K3" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L3" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.7844856922489294</v>
+      </c>
+      <c r="O3" s="5">
+        <v>42</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.022616208860637</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1437791716783996</v>
+      </c>
+      <c r="R3" s="5">
+        <v>42</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2425,12 +2855,1234 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.6001724841333852</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.1010085558963831</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.1078919592197236</v>
+      </c>
+      <c r="E3" s="4">
+        <v>89.58594104308442</v>
+      </c>
+      <c r="F3" s="4">
+        <v>81.89395973154329</v>
+      </c>
+      <c r="G3" s="5">
+        <v>75</v>
+      </c>
+      <c r="H3" s="5">
+        <v>52</v>
+      </c>
+      <c r="I3" s="5">
+        <v>15</v>
+      </c>
+      <c r="J3" s="5">
+        <v>8</v>
+      </c>
+      <c r="K3" s="5">
+        <v>3</v>
+      </c>
+      <c r="L3" s="5">
+        <v>5</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.0435236598237581</v>
+      </c>
+      <c r="O3" s="5">
+        <v>52</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5761201917112531</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.08556859905573942</v>
+      </c>
+      <c r="R3" s="5">
+        <v>52</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>1.148473520582814</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.1592879273323103</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.1256895090637306</v>
+      </c>
+      <c r="E3" s="4">
+        <v>78.68843537414952</v>
+      </c>
+      <c r="F3" s="4">
+        <v>71.92975391498962</v>
+      </c>
+      <c r="G3" s="5">
+        <v>75</v>
+      </c>
+      <c r="H3" s="5">
+        <v>42</v>
+      </c>
+      <c r="I3" s="5">
+        <v>24</v>
+      </c>
+      <c r="J3" s="5">
+        <v>9</v>
+      </c>
+      <c r="K3" s="5">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5">
+        <v>3</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.070510454100875</v>
+      </c>
+      <c r="O3" s="5">
+        <v>42</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.106209746116115</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1358603319067069</v>
+      </c>
+      <c r="R3" s="5">
+        <v>42</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>81.17977528089888</v>
+      </c>
+      <c r="C3" s="3">
+        <v>12.64044943820225</v>
+      </c>
+      <c r="D3" s="3">
+        <v>6.179775280898876</v>
+      </c>
+      <c r="E3" s="3">
+        <v>4.775280898876404</v>
+      </c>
+      <c r="F3" s="3">
+        <v>1.123595505617978</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0.2808988764044944</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.6787518361787102</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.1739509992766186</v>
+      </c>
+      <c r="J3" s="4">
+        <v>1.048920636669855</v>
+      </c>
+      <c r="K3" s="4">
+        <v>84.80528166322721</v>
+      </c>
+      <c r="L3" s="4">
+        <v>82.91500138249992</v>
+      </c>
+      <c r="M3" s="5">
+        <v>356</v>
+      </c>
+      <c r="N3" s="5">
+        <v>1907147.875785828</v>
+      </c>
+      <c r="O3" s="4">
+        <v>33.48458241073509</v>
+      </c>
+      <c r="P3" s="5">
+        <v>56956</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>83.98876404494382</v>
+      </c>
+      <c r="C4" s="3">
+        <v>9.831460674157304</v>
+      </c>
+      <c r="D4" s="3">
+        <v>6.179775280898876</v>
+      </c>
+      <c r="E4" s="3">
+        <v>3.932584269662921</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1.966292134831461</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0.2808988764044944</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.5171199705211874</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.2240181735043436</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.2634531388912088</v>
+      </c>
+      <c r="K4" s="4">
+        <v>83.15944355270238</v>
+      </c>
+      <c r="L4" s="4">
+        <v>81.97549832843326</v>
+      </c>
+      <c r="M4" s="5">
+        <v>356</v>
+      </c>
+      <c r="N4" s="5">
+        <v>4296561.753988266</v>
+      </c>
+      <c r="O4" s="4">
+        <v>62.91088429759087</v>
+      </c>
+      <c r="P4" s="5">
+        <v>68296</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>85.67415730337079</v>
+      </c>
+      <c r="C5" s="3">
+        <v>8.426966292134832</v>
+      </c>
+      <c r="D5" s="3">
+        <v>5.898876404494382</v>
+      </c>
+      <c r="E5" s="3">
+        <v>2.528089887640449</v>
+      </c>
+      <c r="F5" s="3">
+        <v>2.247191011235955</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1.123595505617978</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.4658696093424112</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.1281635334478095</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.5376208099392072</v>
+      </c>
+      <c r="K5" s="4">
+        <v>86.73326072001882</v>
+      </c>
+      <c r="L5" s="4">
+        <v>86.14150516552307</v>
+      </c>
+      <c r="M5" s="5">
+        <v>356</v>
+      </c>
+      <c r="N5" s="5">
+        <v>6543797.536373138</v>
+      </c>
+      <c r="O5" s="4">
+        <v>135.0071701335494</v>
+      </c>
+      <c r="P5" s="5">
+        <v>48470</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>81.17977528089888</v>
+      </c>
+      <c r="C6" s="3">
+        <v>11.23595505617977</v>
+      </c>
+      <c r="D6" s="3">
+        <v>7.584269662921349</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1.966292134831461</v>
+      </c>
+      <c r="F6" s="3">
+        <v>3.370786516853932</v>
+      </c>
+      <c r="G6" s="3">
+        <v>2.247191011235955</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.6114170528744128</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.2881109001003627</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.354620034871405</v>
+      </c>
+      <c r="K6" s="4">
+        <v>84.20287778032568</v>
+      </c>
+      <c r="L6" s="4">
+        <v>82.1855754970714</v>
+      </c>
+      <c r="M6" s="5">
+        <v>356</v>
+      </c>
+      <c r="N6" s="5">
+        <v>4669980.201721191</v>
+      </c>
+      <c r="O6" s="4">
+        <v>85.70500838189712</v>
+      </c>
+      <c r="P6" s="5">
+        <v>54489</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>82.58426966292134</v>
+      </c>
+      <c r="C7" s="3">
+        <v>9.550561797752808</v>
+      </c>
+      <c r="D7" s="3">
+        <v>7.865168539325842</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1.404494382022472</v>
+      </c>
+      <c r="F7" s="3">
+        <v>4.775280898876404</v>
+      </c>
+      <c r="G7" s="3">
+        <v>1.685393258426966</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.7163972417083404</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.09707970410502487</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.6478151090957774</v>
+      </c>
+      <c r="K7" s="4">
+        <v>88.46633035236646</v>
+      </c>
+      <c r="L7" s="4">
+        <v>86.27428801246771</v>
+      </c>
+      <c r="M7" s="5">
+        <v>356</v>
+      </c>
+      <c r="N7" s="5">
+        <v>11382740.66781998</v>
+      </c>
+      <c r="O7" s="4">
+        <v>243.3873731572865</v>
+      </c>
+      <c r="P7" s="5">
+        <v>46768</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>82.58426966292134</v>
+      </c>
+      <c r="C8" s="3">
+        <v>13.48314606741573</v>
+      </c>
+      <c r="D8" s="3">
+        <v>3.932584269662921</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.8426966292134831</v>
+      </c>
+      <c r="F8" s="3">
+        <v>2.808988764044944</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0.2808988764044944</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.5218398567968063</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.1557381840284803</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.4440045873787202</v>
+      </c>
+      <c r="K8" s="4">
+        <v>87.26219139341194</v>
+      </c>
+      <c r="L8" s="4">
+        <v>84.50383957972093</v>
+      </c>
+      <c r="M8" s="5">
+        <v>356</v>
+      </c>
+      <c r="N8" s="5">
+        <v>886133.695602417</v>
+      </c>
+      <c r="O8" s="4">
+        <v>17.60087585115832</v>
+      </c>
+      <c r="P8" s="5">
+        <v>50346</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>78.93258426966293</v>
+      </c>
+      <c r="C9" s="3">
+        <v>9.269662921348315</v>
+      </c>
+      <c r="D9" s="3">
+        <v>11.79775280898876</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3.089887640449438</v>
+      </c>
+      <c r="F9" s="3">
+        <v>7.584269662921349</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1.123595505617978</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.6346138236340285</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.298146743005043</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.3508430942126959</v>
+      </c>
+      <c r="K9" s="4">
+        <v>83.73691049453465</v>
+      </c>
+      <c r="L9" s="4">
+        <v>81.5843764924719</v>
+      </c>
+      <c r="M9" s="5">
+        <v>356</v>
+      </c>
+      <c r="N9" s="5">
+        <v>2093470.83902359</v>
+      </c>
+      <c r="O9" s="4">
+        <v>31.26963567825644</v>
+      </c>
+      <c r="P9" s="5">
+        <v>66949</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>83.98876404494382</v>
+      </c>
+      <c r="C10" s="3">
+        <v>8.426966292134832</v>
+      </c>
+      <c r="D10" s="3">
+        <v>7.584269662921349</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1.404494382022472</v>
+      </c>
+      <c r="F10" s="3">
+        <v>5.898876404494382</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0.2808988764044944</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.3989153279532354</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.133436955355965</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.1830072752836795</v>
+      </c>
+      <c r="K10" s="4">
+        <v>84.94124054116031</v>
+      </c>
+      <c r="L10" s="4">
+        <v>84.25854007993415</v>
+      </c>
+      <c r="M10" s="5">
+        <v>356</v>
+      </c>
+      <c r="N10" s="5">
+        <v>3715791.021585464</v>
+      </c>
+      <c r="O10" s="4">
+        <v>90.30966147977797</v>
+      </c>
+      <c r="P10" s="5">
+        <v>41145</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>83.98876404494382</v>
+      </c>
+      <c r="C11" s="3">
+        <v>8.707865168539326</v>
+      </c>
+      <c r="D11" s="3">
+        <v>7.303370786516854</v>
+      </c>
+      <c r="E11" s="3">
+        <v>4.49438202247191</v>
+      </c>
+      <c r="F11" s="3">
+        <v>2.247191011235955</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0.5617977528089888</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.7143248841147365</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.1784030782666599</v>
+      </c>
+      <c r="J11" s="4">
+        <v>1.301526528687049</v>
+      </c>
+      <c r="K11" s="4">
+        <v>86.16926545899265</v>
+      </c>
+      <c r="L11" s="4">
+        <v>84.59624714073914</v>
+      </c>
+      <c r="M11" s="5">
+        <v>356</v>
+      </c>
+      <c r="N11" s="5">
+        <v>2472570.067644119</v>
+      </c>
+      <c r="O11" s="4">
+        <v>41.27416398431074</v>
+      </c>
+      <c r="P11" s="5">
+        <v>59906</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>82.02247191011236</v>
+      </c>
+      <c r="C12" s="3">
+        <v>12.92134831460674</v>
+      </c>
+      <c r="D12" s="3">
+        <v>5.056179775280898</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2.247191011235955</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1.966292134831461</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.8426966292134831</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.5821381226186757</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.1733705104181938</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.3815371985045769</v>
+      </c>
+      <c r="K12" s="4">
+        <v>83.9401322326689</v>
+      </c>
+      <c r="L12" s="4">
+        <v>83.06811326445929</v>
+      </c>
+      <c r="M12" s="5">
+        <v>356</v>
+      </c>
+      <c r="N12" s="5">
+        <v>1000044.785499573</v>
+      </c>
+      <c r="O12" s="4">
+        <v>21.19277751758016</v>
+      </c>
+      <c r="P12" s="5">
+        <v>47188</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>81.46067415730337</v>
+      </c>
+      <c r="C13" s="3">
+        <v>12.92134831460674</v>
+      </c>
+      <c r="D13" s="3">
+        <v>5.617977528089887</v>
+      </c>
+      <c r="E13" s="3">
+        <v>3.370786516853932</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1.966292134831461</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0.2808988764044944</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.6438580988563941</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.09962091943985511</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.7057919136884455</v>
+      </c>
+      <c r="K13" s="4">
+        <v>86.83864557058814</v>
+      </c>
+      <c r="L13" s="4">
+        <v>84.38277656285341</v>
+      </c>
+      <c r="M13" s="5">
+        <v>356</v>
+      </c>
+      <c r="N13" s="5">
+        <v>4975748.042583466</v>
+      </c>
+      <c r="O13" s="4">
+        <v>77.85554752907942</v>
+      </c>
+      <c r="P13" s="5">
+        <v>63910</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>65.33333333333333</v>
+      </c>
+      <c r="C14" s="3">
+        <v>21.33333333333334</v>
+      </c>
+      <c r="D14" s="3">
+        <v>13.33333333333333</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="F14" s="3">
+        <v>12</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.654106167967941</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.06310252416999571</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.09037224252351204</v>
+      </c>
+      <c r="K14" s="4">
+        <v>90.18231292517036</v>
+      </c>
+      <c r="L14" s="4">
+        <v>80.54213273676372</v>
+      </c>
+      <c r="M14" s="5">
+        <v>75</v>
+      </c>
+      <c r="N14" s="5">
+        <v>5024593.505620956</v>
+      </c>
+      <c r="O14" s="4">
+        <v>345.0483110576128</v>
+      </c>
+      <c r="P14" s="5">
+        <v>14562</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>56.00000000000001</v>
+      </c>
+      <c r="C15" s="3">
+        <v>32</v>
+      </c>
+      <c r="D15" s="3">
+        <v>12</v>
+      </c>
+      <c r="E15" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="F15" s="3">
+        <v>5.333333333333334</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>1.022616208860637</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.1437791716783996</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.1173065125753003</v>
+      </c>
+      <c r="K15" s="4">
+        <v>80.24943310657621</v>
+      </c>
+      <c r="L15" s="4">
+        <v>73.03758389261823</v>
+      </c>
+      <c r="M15" s="5">
+        <v>75</v>
+      </c>
+      <c r="N15" s="5">
+        <v>5689963.02986145</v>
+      </c>
+      <c r="O15" s="4">
+        <v>331.0427641297097</v>
+      </c>
+      <c r="P15" s="5">
+        <v>17188</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>69.33333333333334</v>
+      </c>
+      <c r="C16" s="3">
+        <v>20</v>
+      </c>
+      <c r="D16" s="3">
+        <v>10.66666666666667</v>
+      </c>
+      <c r="E16" s="3">
+        <v>4</v>
+      </c>
+      <c r="F16" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.5761201917112531</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.08556859905573942</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.09711111879731985</v>
+      </c>
+      <c r="K16" s="4">
+        <v>89.58594104308442</v>
+      </c>
+      <c r="L16" s="4">
+        <v>81.89395973154329</v>
+      </c>
+      <c r="M16" s="5">
+        <v>75</v>
+      </c>
+      <c r="N16" s="5">
+        <v>1012192.121982574</v>
+      </c>
+      <c r="O16" s="4">
+        <v>98.49101118834042</v>
+      </c>
+      <c r="P16" s="5">
+        <v>10277</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>56.00000000000001</v>
+      </c>
+      <c r="C17" s="3">
+        <v>32</v>
+      </c>
+      <c r="D17" s="3">
+        <v>12</v>
+      </c>
+      <c r="E17" s="3">
+        <v>8</v>
+      </c>
+      <c r="F17" s="3">
+        <v>4</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>1.106209746116115</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.1358603319067069</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.1349643669450107</v>
+      </c>
+      <c r="K17" s="4">
+        <v>78.68843537414952</v>
+      </c>
+      <c r="L17" s="4">
+        <v>71.92975391498962</v>
+      </c>
+      <c r="M17" s="5">
+        <v>75</v>
+      </c>
+      <c r="N17" s="5">
+        <v>2151973.101377487</v>
+      </c>
+      <c r="O17" s="4">
+        <v>98.97769760728025</v>
+      </c>
+      <c r="P17" s="5">
+        <v>21742</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2544,10 +4196,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
@@ -2588,7 +4240,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
         <v>6</v>
@@ -2632,10 +4284,10 @@
         <v>0</v>
       </c>
       <c r="K5" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
@@ -2676,7 +4328,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6" s="5">
         <v>11</v>
@@ -2720,10 +4372,10 @@
         <v>0</v>
       </c>
       <c r="K7" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L7" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
@@ -2764,7 +4416,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L8" s="5">
         <v>7</v>
@@ -2808,16 +4460,16 @@
         <v>0</v>
       </c>
       <c r="K9" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L9" s="5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M9" s="5">
         <v>0</v>
       </c>
       <c r="N9" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="25" customHeight="1">
@@ -2852,16 +4504,16 @@
         <v>0</v>
       </c>
       <c r="K10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M10" s="5">
         <v>0</v>
       </c>
       <c r="N10" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="25" customHeight="1">
@@ -2896,10 +4548,10 @@
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L11" s="5">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="M11" s="5">
         <v>0</v>
@@ -2940,16 +4592,16 @@
         <v>3</v>
       </c>
       <c r="K12" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L12" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M12" s="5">
         <v>0</v>
       </c>
       <c r="N12" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="25" customHeight="1">
@@ -2984,10 +4636,10 @@
         <v>0</v>
       </c>
       <c r="K13" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L13" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M13" s="5">
         <v>0</v>
@@ -3072,7 +4724,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" s="5">
         <v>4</v>
@@ -3119,7 +4771,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M16" s="5">
         <v>0</v>
@@ -3160,10 +4812,10 @@
         <v>0</v>
       </c>
       <c r="K17" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M17" s="5">
         <v>0</v>
@@ -3185,9 +4837,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>289</v>
+      </c>
+      <c r="C3" s="5">
+        <v>45</v>
+      </c>
+      <c r="D3" s="5">
+        <v>22</v>
+      </c>
+      <c r="E3" s="5">
+        <v>17</v>
+      </c>
+      <c r="F3" s="5">
+        <v>4</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>17</v>
+      </c>
+      <c r="I3" s="5">
+        <v>17</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>2</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>299</v>
+      </c>
+      <c r="C4" s="5">
+        <v>35</v>
+      </c>
+      <c r="D4" s="5">
+        <v>22</v>
+      </c>
+      <c r="E4" s="5">
+        <v>14</v>
+      </c>
+      <c r="F4" s="5">
+        <v>7</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>14</v>
+      </c>
+      <c r="I4" s="5">
+        <v>14</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>6</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>305</v>
+      </c>
+      <c r="C5" s="5">
+        <v>30</v>
+      </c>
+      <c r="D5" s="5">
+        <v>21</v>
+      </c>
+      <c r="E5" s="5">
+        <v>9</v>
+      </c>
+      <c r="F5" s="5">
+        <v>8</v>
+      </c>
+      <c r="G5" s="5">
+        <v>4</v>
+      </c>
+      <c r="H5" s="5">
+        <v>9</v>
+      </c>
+      <c r="I5" s="5">
+        <v>9</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5">
+        <v>5</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>289</v>
+      </c>
+      <c r="C6" s="5">
+        <v>40</v>
+      </c>
+      <c r="D6" s="5">
+        <v>27</v>
+      </c>
+      <c r="E6" s="5">
+        <v>7</v>
+      </c>
+      <c r="F6" s="5">
+        <v>12</v>
+      </c>
+      <c r="G6" s="5">
+        <v>8</v>
+      </c>
+      <c r="H6" s="5">
+        <v>7</v>
+      </c>
+      <c r="I6" s="5">
+        <v>7</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>11</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>294</v>
+      </c>
+      <c r="C7" s="5">
+        <v>34</v>
+      </c>
+      <c r="D7" s="5">
+        <v>28</v>
+      </c>
+      <c r="E7" s="5">
+        <v>5</v>
+      </c>
+      <c r="F7" s="5">
+        <v>17</v>
+      </c>
+      <c r="G7" s="5">
+        <v>6</v>
+      </c>
+      <c r="H7" s="5">
+        <v>5</v>
+      </c>
+      <c r="I7" s="5">
+        <v>5</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>1</v>
+      </c>
+      <c r="L7" s="5">
+        <v>14</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>294</v>
+      </c>
+      <c r="C8" s="5">
+        <v>48</v>
+      </c>
+      <c r="D8" s="5">
+        <v>14</v>
+      </c>
+      <c r="E8" s="5">
+        <v>3</v>
+      </c>
+      <c r="F8" s="5">
+        <v>10</v>
+      </c>
+      <c r="G8" s="5">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5">
+        <v>3</v>
+      </c>
+      <c r="I8" s="5">
+        <v>3</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>1</v>
+      </c>
+      <c r="L8" s="5">
+        <v>7</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>281</v>
+      </c>
+      <c r="C9" s="5">
+        <v>33</v>
+      </c>
+      <c r="D9" s="5">
+        <v>42</v>
+      </c>
+      <c r="E9" s="5">
+        <v>11</v>
+      </c>
+      <c r="F9" s="5">
+        <v>27</v>
+      </c>
+      <c r="G9" s="5">
+        <v>4</v>
+      </c>
+      <c r="H9" s="5">
+        <v>11</v>
+      </c>
+      <c r="I9" s="5">
+        <v>11</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>1</v>
+      </c>
+      <c r="L9" s="5">
+        <v>23</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>299</v>
+      </c>
+      <c r="C10" s="5">
+        <v>30</v>
+      </c>
+      <c r="D10" s="5">
+        <v>27</v>
+      </c>
+      <c r="E10" s="5">
+        <v>5</v>
+      </c>
+      <c r="F10" s="5">
+        <v>21</v>
+      </c>
+      <c r="G10" s="5">
+        <v>1</v>
+      </c>
+      <c r="H10" s="5">
+        <v>5</v>
+      </c>
+      <c r="I10" s="5">
+        <v>5</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>17</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>299</v>
+      </c>
+      <c r="C11" s="5">
+        <v>31</v>
+      </c>
+      <c r="D11" s="5">
+        <v>26</v>
+      </c>
+      <c r="E11" s="5">
+        <v>16</v>
+      </c>
+      <c r="F11" s="5">
+        <v>8</v>
+      </c>
+      <c r="G11" s="5">
+        <v>2</v>
+      </c>
+      <c r="H11" s="5">
+        <v>16</v>
+      </c>
+      <c r="I11" s="5">
+        <v>16</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>6</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>292</v>
+      </c>
+      <c r="C12" s="5">
+        <v>46</v>
+      </c>
+      <c r="D12" s="5">
+        <v>18</v>
+      </c>
+      <c r="E12" s="5">
+        <v>8</v>
+      </c>
+      <c r="F12" s="5">
+        <v>7</v>
+      </c>
+      <c r="G12" s="5">
+        <v>3</v>
+      </c>
+      <c r="H12" s="5">
+        <v>8</v>
+      </c>
+      <c r="I12" s="5">
+        <v>5</v>
+      </c>
+      <c r="J12" s="5">
+        <v>3</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>7</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>290</v>
+      </c>
+      <c r="C13" s="5">
+        <v>46</v>
+      </c>
+      <c r="D13" s="5">
+        <v>20</v>
+      </c>
+      <c r="E13" s="5">
+        <v>12</v>
+      </c>
+      <c r="F13" s="5">
+        <v>7</v>
+      </c>
+      <c r="G13" s="5">
+        <v>1</v>
+      </c>
+      <c r="H13" s="5">
+        <v>12</v>
+      </c>
+      <c r="I13" s="5">
+        <v>12</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>1</v>
+      </c>
+      <c r="L13" s="5">
+        <v>4</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>49</v>
+      </c>
+      <c r="C14" s="5">
+        <v>16</v>
+      </c>
+      <c r="D14" s="5">
+        <v>10</v>
+      </c>
+      <c r="E14" s="5">
+        <v>1</v>
+      </c>
+      <c r="F14" s="5">
+        <v>9</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>1</v>
+      </c>
+      <c r="I14" s="5">
+        <v>1</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>1</v>
+      </c>
+      <c r="L14" s="5">
+        <v>8</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>42</v>
+      </c>
+      <c r="C15" s="5">
+        <v>24</v>
+      </c>
+      <c r="D15" s="5">
+        <v>9</v>
+      </c>
+      <c r="E15" s="5">
+        <v>5</v>
+      </c>
+      <c r="F15" s="5">
+        <v>4</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>5</v>
+      </c>
+      <c r="I15" s="5">
+        <v>5</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>4</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>52</v>
+      </c>
+      <c r="C16" s="5">
+        <v>15</v>
+      </c>
+      <c r="D16" s="5">
+        <v>8</v>
+      </c>
+      <c r="E16" s="5">
+        <v>3</v>
+      </c>
+      <c r="F16" s="5">
+        <v>5</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>3</v>
+      </c>
+      <c r="I16" s="5">
+        <v>3</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>5</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>42</v>
+      </c>
+      <c r="C17" s="5">
+        <v>24</v>
+      </c>
+      <c r="D17" s="5">
+        <v>9</v>
+      </c>
+      <c r="E17" s="5">
+        <v>6</v>
+      </c>
+      <c r="F17" s="5">
+        <v>3</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>6</v>
+      </c>
+      <c r="I17" s="5">
+        <v>6</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>3</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3198,9 +5605,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3234,8 +5647,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3257,10 +5678,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>1.179345407772073</v>
@@ -3298,9 +5737,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>0.1336003821783347</v>
+      </c>
+      <c r="O3" s="5">
+        <v>41</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.235903580001828</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3166933659077159</v>
+      </c>
+      <c r="R3" s="5">
+        <v>41</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3311,14 +5768,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3329,9 +5787,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3365,8 +5829,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3388,10 +5860,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>1.151286724734507</v>
@@ -3429,9 +5919,27 @@
       <c r="M3" s="5">
         <v>1</v>
       </c>
+      <c r="N3" s="4">
+        <v>1.293056276668066</v>
+      </c>
+      <c r="O3" s="5">
+        <v>42</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.129241700869396</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3110208121329153</v>
+      </c>
+      <c r="R3" s="5">
+        <v>42</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3442,14 +5950,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3460,9 +5969,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3496,8 +6011,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3519,10 +6042,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.8717153954389839</v>
@@ -3560,9 +6101,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>0.4022950923644838</v>
+      </c>
+      <c r="O3" s="5">
+        <v>52</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7989413367793646</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1285113927684899</v>
+      </c>
+      <c r="R3" s="5">
+        <v>52</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3573,14 +6132,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3591,9 +6151,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3627,8 +6193,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3650,10 +6224,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>1.048168436743803</v>
@@ -3691,9 +6283,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>0.5950897031702944</v>
+      </c>
+      <c r="O3" s="5">
+        <v>41</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.104634351381236</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2629495203092853</v>
+      </c>
+      <c r="R3" s="5">
+        <v>41</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3704,14 +6314,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3722,9 +6333,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3758,8 +6375,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3781,10 +6406,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>1.188495318554024</v>
@@ -3822,9 +6465,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>0.7049297103247132</v>
+      </c>
+      <c r="O3" s="5">
+        <v>45</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.132638735487714</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.151185239950358</v>
+      </c>
+      <c r="R3" s="5">
+        <v>45</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3835,268 +6496,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1.083794477503847</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.9931274365916724</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1.025895669623709</v>
-      </c>
-      <c r="E3" s="4">
-        <v>82.70249433106626</v>
-      </c>
-      <c r="F3" s="4">
-        <v>73.44310216256507</v>
-      </c>
-      <c r="G3" s="5">
-        <v>75</v>
-      </c>
-      <c r="H3" s="5">
-        <v>44</v>
-      </c>
-      <c r="I3" s="5">
-        <v>26</v>
-      </c>
-      <c r="J3" s="5">
-        <v>5</v>
-      </c>
-      <c r="K3" s="5">
-        <v>2</v>
-      </c>
-      <c r="L3" s="5">
-        <v>3</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1.166632073732801</v>
-      </c>
-      <c r="C3" s="4">
-        <v>1.068705100845164</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1.038358367027022</v>
-      </c>
-      <c r="E3" s="4">
-        <v>78.26848072562331</v>
-      </c>
-      <c r="F3" s="4">
-        <v>68.55615212527937</v>
-      </c>
-      <c r="G3" s="5">
-        <v>75</v>
-      </c>
-      <c r="H3" s="5">
-        <v>37</v>
-      </c>
-      <c r="I3" s="5">
-        <v>21</v>
-      </c>
-      <c r="J3" s="5">
-        <v>17</v>
-      </c>
-      <c r="K3" s="5">
-        <v>5</v>
-      </c>
-      <c r="L3" s="5">
-        <v>12</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/MandalMetal2024.xlsx
+++ b/public/downloads/MandalMetal2024.xlsx
@@ -1551,13 +1551,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.9931274365916724</v>
+        <v>0.9723079750831474</v>
       </c>
       <c r="O3" s="5">
         <v>44</v>
       </c>
       <c r="P3" s="4">
-        <v>0.9737027997801503</v>
+        <v>0.9656526079968538</v>
       </c>
       <c r="Q3" s="4">
         <v>0.2363680394090351</v>
@@ -1733,16 +1733,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>1.068705100845164</v>
+        <v>1.091117296070564</v>
       </c>
       <c r="O3" s="5">
         <v>37</v>
       </c>
       <c r="P3" s="4">
-        <v>1.236968312849004</v>
+        <v>1.24682967874818</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2947446408733825</v>
+        <v>0.2941389058672906</v>
       </c>
       <c r="R3" s="5">
         <v>37</v>
@@ -1915,16 +1915,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3351135331373916</v>
+        <v>0.2838060835744045</v>
       </c>
       <c r="O3" s="5">
         <v>49</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7691834243171369</v>
+        <v>0.7461426173289564</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1406108465487569</v>
+        <v>0.1283803030032908</v>
       </c>
       <c r="R3" s="5">
         <v>49</v>
@@ -2097,16 +2097,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>1.314934356725868</v>
+        <v>1.299359729338363</v>
       </c>
       <c r="O3" s="5">
         <v>46</v>
       </c>
       <c r="P3" s="4">
-        <v>0.9812917549114208</v>
+        <v>0.9743165177981707</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2288222077984503</v>
+        <v>0.2272683254233178</v>
       </c>
       <c r="R3" s="5">
         <v>46</v>
@@ -2279,16 +2279,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.166217374891215</v>
+        <v>0.1415560373168887</v>
       </c>
       <c r="O3" s="5">
         <v>41</v>
       </c>
       <c r="P3" s="4">
-        <v>1.064570208689268</v>
+        <v>1.052611542163017</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1708219413926307</v>
+        <v>0.1693971971989308</v>
       </c>
       <c r="R3" s="5">
         <v>41</v>
@@ -2461,16 +2461,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.7130821895449037</v>
+        <v>0.6678698479248055</v>
       </c>
       <c r="O3" s="5">
         <v>39</v>
       </c>
       <c r="P3" s="4">
-        <v>1.046928913703544</v>
+        <v>1.021129783788284</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1292336152671493</v>
+        <v>0.120767626957636</v>
       </c>
       <c r="R3" s="5">
         <v>39</v>
@@ -2643,16 +2643,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.01348957171501533</v>
+        <v>-0.02251313603872518</v>
       </c>
       <c r="O3" s="5">
         <v>49</v>
       </c>
       <c r="P3" s="4">
-        <v>0.654106167967941</v>
+        <v>0.6507431734819119</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.06310252416999571</v>
+        <v>0.06237478860503398</v>
       </c>
       <c r="R3" s="5">
         <v>49</v>
@@ -2825,16 +2825,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.7844856922489294</v>
+        <v>-0.8314550656457698</v>
       </c>
       <c r="O3" s="5">
         <v>42</v>
       </c>
       <c r="P3" s="4">
-        <v>1.022616208860637</v>
+        <v>1.000133258659555</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1437791716783996</v>
+        <v>0.1360622803314284</v>
       </c>
       <c r="R3" s="5">
         <v>42</v>
@@ -3007,16 +3007,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.0435236598237581</v>
+        <v>-0.07612082698966915</v>
       </c>
       <c r="O3" s="5">
         <v>52</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5761201917112531</v>
+        <v>0.5652721828368057</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.08556859905573942</v>
+        <v>0.08327935631346055</v>
       </c>
       <c r="R3" s="5">
         <v>52</v>
@@ -3189,16 +3189,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.070510454100875</v>
+        <v>-0.08743571998716959</v>
       </c>
       <c r="O3" s="5">
         <v>42</v>
       </c>
       <c r="P3" s="4">
-        <v>1.106209746116115</v>
+        <v>1.09808237598831</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1358603319067069</v>
+        <v>0.1338396291183697</v>
       </c>
       <c r="R3" s="5">
         <v>42</v>
@@ -3335,13 +3335,13 @@
         <v>0.2808988764044944</v>
       </c>
       <c r="H3" s="4">
-        <v>0.6787518361787102</v>
+        <v>0.6731353293165627</v>
       </c>
       <c r="I3" s="4">
-        <v>0.1739509992766186</v>
+        <v>0.1713309287923364</v>
       </c>
       <c r="J3" s="4">
-        <v>1.048920636669855</v>
+        <v>1.04610748816385</v>
       </c>
       <c r="K3" s="4">
         <v>84.80528166322721</v>
@@ -3385,13 +3385,13 @@
         <v>0.2808988764044944</v>
       </c>
       <c r="H4" s="4">
-        <v>0.5171199705211874</v>
+        <v>0.5072696022233704</v>
       </c>
       <c r="I4" s="4">
-        <v>0.2240181735043436</v>
+        <v>0.2199384057145364</v>
       </c>
       <c r="J4" s="4">
-        <v>0.2634531388912088</v>
+        <v>0.2601904338697159</v>
       </c>
       <c r="K4" s="4">
         <v>83.15944355270238</v>
@@ -3435,13 +3435,13 @@
         <v>1.123595505617978</v>
       </c>
       <c r="H5" s="4">
-        <v>0.4658696093424112</v>
+        <v>0.444544152989176</v>
       </c>
       <c r="I5" s="4">
-        <v>0.1281635334478095</v>
+        <v>0.1103060082720832</v>
       </c>
       <c r="J5" s="4">
-        <v>0.5376208099392072</v>
+        <v>0.5284074592959593</v>
       </c>
       <c r="K5" s="4">
         <v>86.73326072001882</v>
@@ -3467,13 +3467,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="3">
-        <v>81.17977528089888</v>
+        <v>80.89887640449437</v>
       </c>
       <c r="C6" s="3">
         <v>11.23595505617977</v>
       </c>
       <c r="D6" s="3">
-        <v>7.584269662921349</v>
+        <v>7.865168539325842</v>
       </c>
       <c r="E6" s="3">
         <v>1.966292134831461</v>
@@ -3482,16 +3482,16 @@
         <v>3.370786516853932</v>
       </c>
       <c r="G6" s="3">
-        <v>2.247191011235955</v>
+        <v>2.528089887640449</v>
       </c>
       <c r="H6" s="4">
-        <v>0.6114170528744128</v>
+        <v>0.5758467562739867</v>
       </c>
       <c r="I6" s="4">
-        <v>0.2881109001003627</v>
+        <v>0.2585057129292394</v>
       </c>
       <c r="J6" s="4">
-        <v>0.354620034871405</v>
+        <v>0.3383771182102645</v>
       </c>
       <c r="K6" s="4">
         <v>84.20287778032568</v>
@@ -3535,13 +3535,13 @@
         <v>1.685393258426966</v>
       </c>
       <c r="H7" s="4">
-        <v>0.7163972417083404</v>
+        <v>0.7010168764692963</v>
       </c>
       <c r="I7" s="4">
-        <v>0.09707970410502487</v>
+        <v>0.08542372950153332</v>
       </c>
       <c r="J7" s="4">
-        <v>0.6478151090957774</v>
+        <v>0.6481520307890185</v>
       </c>
       <c r="K7" s="4">
         <v>88.46633035236646</v>
@@ -3585,13 +3585,13 @@
         <v>0.2808988764044944</v>
       </c>
       <c r="H8" s="4">
-        <v>0.5218398567968063</v>
+        <v>0.5179745661561608</v>
       </c>
       <c r="I8" s="4">
-        <v>0.1557381840284803</v>
+        <v>0.1537726284357617</v>
       </c>
       <c r="J8" s="4">
-        <v>0.4440045873787202</v>
+        <v>0.4451636200460133</v>
       </c>
       <c r="K8" s="4">
         <v>87.26219139341194</v>
@@ -3617,13 +3617,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="3">
-        <v>78.93258426966293</v>
+        <v>78.37078651685393</v>
       </c>
       <c r="C9" s="3">
         <v>9.269662921348315</v>
       </c>
       <c r="D9" s="3">
-        <v>11.79775280898876</v>
+        <v>12.35955056179775</v>
       </c>
       <c r="E9" s="3">
         <v>3.089887640449438</v>
@@ -3632,16 +3632,16 @@
         <v>7.584269662921349</v>
       </c>
       <c r="G9" s="3">
-        <v>1.123595505617978</v>
+        <v>1.685393258426966</v>
       </c>
       <c r="H9" s="4">
-        <v>0.6346138236340285</v>
+        <v>0.6230858566916208</v>
       </c>
       <c r="I9" s="4">
-        <v>0.298146743005043</v>
+        <v>0.275337250489957</v>
       </c>
       <c r="J9" s="4">
-        <v>0.3508430942126959</v>
+        <v>0.3483371478850698</v>
       </c>
       <c r="K9" s="4">
         <v>83.73691049453465</v>
@@ -3685,13 +3685,13 @@
         <v>0.2808988764044944</v>
       </c>
       <c r="H10" s="4">
-        <v>0.3989153279532354</v>
+        <v>0.3916151369593193</v>
       </c>
       <c r="I10" s="4">
-        <v>0.133436955355965</v>
+        <v>0.1297912787528605</v>
       </c>
       <c r="J10" s="4">
-        <v>0.1830072752836795</v>
+        <v>0.1847118020067204</v>
       </c>
       <c r="K10" s="4">
         <v>84.94124054116031</v>
@@ -3735,13 +3735,13 @@
         <v>0.5617977528089888</v>
       </c>
       <c r="H11" s="4">
-        <v>0.7143248841147365</v>
+        <v>0.7109437437664591</v>
       </c>
       <c r="I11" s="4">
-        <v>0.1784030782666599</v>
+        <v>0.1756469447927925</v>
       </c>
       <c r="J11" s="4">
-        <v>1.301526528687049</v>
+        <v>1.298941020965318</v>
       </c>
       <c r="K11" s="4">
         <v>86.16926545899265</v>
@@ -3785,13 +3785,13 @@
         <v>0.8426966292134831</v>
       </c>
       <c r="H12" s="4">
-        <v>0.5821381226186757</v>
+        <v>0.5672085496837274</v>
       </c>
       <c r="I12" s="4">
-        <v>0.1733705104181938</v>
+        <v>0.1606163296727591</v>
       </c>
       <c r="J12" s="4">
-        <v>0.3815371985045769</v>
+        <v>0.3766948530206104</v>
       </c>
       <c r="K12" s="4">
         <v>83.9401322326689</v>
@@ -3835,13 +3835,13 @@
         <v>0.2808988764044944</v>
       </c>
       <c r="H13" s="4">
-        <v>0.6438580988563941</v>
+        <v>0.6369831639213093</v>
       </c>
       <c r="I13" s="4">
-        <v>0.09962091943985511</v>
+        <v>0.09720338039091438</v>
       </c>
       <c r="J13" s="4">
-        <v>0.7057919136884455</v>
+        <v>0.7086381903029759</v>
       </c>
       <c r="K13" s="4">
         <v>86.83864557058814</v>
@@ -3885,13 +3885,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.654106167967941</v>
+        <v>0.6507431734819119</v>
       </c>
       <c r="I14" s="4">
-        <v>0.06310252416999571</v>
+        <v>0.06237478860503398</v>
       </c>
       <c r="J14" s="4">
-        <v>0.09037224252351204</v>
+        <v>0.0914367703726295</v>
       </c>
       <c r="K14" s="4">
         <v>90.18231292517036</v>
@@ -3935,13 +3935,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>1.022616208860637</v>
+        <v>1.000133258659555</v>
       </c>
       <c r="I15" s="4">
-        <v>0.1437791716783996</v>
+        <v>0.1360622803314284</v>
       </c>
       <c r="J15" s="4">
-        <v>0.1173065125753003</v>
+        <v>0.1217633544414619</v>
       </c>
       <c r="K15" s="4">
         <v>80.24943310657621</v>
@@ -3985,13 +3985,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.5761201917112531</v>
+        <v>0.5652721828368057</v>
       </c>
       <c r="I16" s="4">
-        <v>0.08556859905573942</v>
+        <v>0.08327935631346055</v>
       </c>
       <c r="J16" s="4">
-        <v>0.09711111879731985</v>
+        <v>0.1023606063630837</v>
       </c>
       <c r="K16" s="4">
         <v>89.58594104308442</v>
@@ -4035,13 +4035,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>1.106209746116115</v>
+        <v>1.09808237598831</v>
       </c>
       <c r="I17" s="4">
-        <v>0.1358603319067069</v>
+        <v>0.1338396291183697</v>
       </c>
       <c r="J17" s="4">
-        <v>0.1349643669450107</v>
+        <v>0.141335315052959</v>
       </c>
       <c r="K17" s="4">
         <v>78.68843537414952</v>
@@ -5056,13 +5056,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="5">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C6" s="5">
         <v>40</v>
       </c>
       <c r="D6" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E6" s="5">
         <v>7</v>
@@ -5071,7 +5071,7 @@
         <v>12</v>
       </c>
       <c r="G6" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6" s="5">
         <v>7</v>
@@ -5188,13 +5188,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="5">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C9" s="5">
         <v>33</v>
       </c>
       <c r="D9" s="5">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E9" s="5">
         <v>11</v>
@@ -5203,7 +5203,7 @@
         <v>27</v>
       </c>
       <c r="G9" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H9" s="5">
         <v>11</v>
@@ -5738,16 +5738,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1336003821783347</v>
+        <v>0.09963453755369756</v>
       </c>
       <c r="O3" s="5">
         <v>41</v>
       </c>
       <c r="P3" s="4">
-        <v>1.235903580001828</v>
+        <v>1.218273687027861</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3166933659077159</v>
+        <v>0.3126103596684519</v>
       </c>
       <c r="R3" s="5">
         <v>41</v>
@@ -5920,16 +5920,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>1.293056276668066</v>
+        <v>1.239839873144525</v>
       </c>
       <c r="O3" s="5">
         <v>42</v>
       </c>
       <c r="P3" s="4">
-        <v>1.129241700869396</v>
+        <v>1.104031405638408</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3110208121329153</v>
+        <v>0.3078153162746471</v>
       </c>
       <c r="R3" s="5">
         <v>42</v>
@@ -6102,16 +6102,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.4022950923644838</v>
+        <v>0.3552593350049875</v>
       </c>
       <c r="O3" s="5">
         <v>52</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7989413367793646</v>
+        <v>0.7811919825599413</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1285113927684899</v>
+        <v>0.1237156399379449</v>
       </c>
       <c r="R3" s="5">
         <v>52</v>
@@ -6284,16 +6284,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.5950897031702944</v>
+        <v>0.5521042600109922</v>
       </c>
       <c r="O3" s="5">
         <v>41</v>
       </c>
       <c r="P3" s="4">
-        <v>1.104634351381236</v>
+        <v>1.086801851899478</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2629495203092853</v>
+        <v>0.2617818577153138</v>
       </c>
       <c r="R3" s="5">
         <v>41</v>
@@ -6466,16 +6466,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.7049297103247132</v>
+        <v>0.6569920793627926</v>
       </c>
       <c r="O3" s="5">
         <v>45</v>
       </c>
       <c r="P3" s="4">
-        <v>1.132638735487714</v>
+        <v>1.108454034833741</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.151185239950358</v>
+        <v>0.1428358261683492</v>
       </c>
       <c r="R3" s="5">
         <v>45</v>
